--- a/Trắc nghiệm ôn luyện/BA Functional/multiple_choice_sample_template_AGILE_USER_STORIES.xlsx
+++ b/Trắc nghiệm ôn luyện/BA Functional/multiple_choice_sample_template_AGILE_USER_STORIES.xlsx
@@ -453,19 +453,19 @@
         <v>Scrum Master là người hỗ trợ (Servant Leader), giúp Scrum Team làm việc hiệu quả bằng cách loại bỏ các rào cản và đảm bảo tuân thủ quy trình Scrum.</v>
       </c>
       <c r="E2" t="str">
-        <v>Đóng vai trò là người hỗ trợ, loại bỏ trở ngại và bảo vệ quy trình làm việc của team — servant leader</v>
+        <v>Đứng ra phân chia công việc hàng ngày và chấm công cho các thành viên — quản lý hành chính</v>
       </c>
       <c r="F2" t="str">
-        <v>Đứng ra phân chia công việc hàng ngày và chấm công cho các thành viên — quản lý hành chính</v>
+        <v>Trực tiếp thương lượng tiến độ và ký hợp đồng kinh doanh với khách hàng — account manager</v>
       </c>
       <c r="G2" t="str">
         <v>Chịu trách nhiệm thiết kế kiến trúc kỹ thuật và viết code chính của dự án — tech lead</v>
       </c>
       <c r="H2" t="str">
-        <v>Trực tiếp thương lượng tiến độ và ký hợp đồng kinh doanh với khách hàng — account manager</v>
+        <v>Đóng vai trò là người hỗ trợ, loại bỏ trở ngại và bảo vệ quy trình làm việc của team — servant leader</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -482,7 +482,7 @@
         <v>Product Backlog là danh sách duy nhất các yêu cầu, tính năng được sắp xếp theo thứ tự ưu tiên nhằm phát triển sản phẩm.</v>
       </c>
       <c r="E3" t="str">
-        <v>Danh sách ưu tiên các tính năng, yêu cầu và công việc cần thực hiện cho sản phẩm — danh sách công việc tích lũy</v>
+        <v>Bản kế hoạch kiểm thử chi tiết bao gồm tất cả các kịch bản test lỗi — kế hoạch kiểm thử</v>
       </c>
       <c r="F3" t="str">
         <v>Tài liệu báo cáo tài chính và chi phí nhân sự hàng tháng của dự án — báo cáo tài chính</v>
@@ -491,10 +491,10 @@
         <v>Sơ đồ thiết kế cơ sở dữ liệu chi tiết của toàn bộ hệ thống — sơ đồ kỹ thuật</v>
       </c>
       <c r="H3" t="str">
-        <v>Bản kế hoạch kiểm thử chi tiết bao gồm tất cả các kịch bản test lỗi — kế hoạch kiểm thử</v>
+        <v>Danh sách ưu tiên các tính năng, yêu cầu và công việc cần thực hiện cho sản phẩm — danh sách công việc tích lũy</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         <v>Sprint là một khung thời gian lặp đi lặp lại có độ dài cố định (thường từ 1-4 tuần) để tạo ra một phần tăng trưởng sản phẩm có thể bàn giao.</v>
       </c>
       <c r="E4" t="str">
+        <v>Quy trình kiểm thử hiệu năng tải trang web trước khi bàn giao cho khách hàng — kiểm thử tải</v>
+      </c>
+      <c r="F4" t="str">
         <v>Một khoảng thời gian cố định (thường từ 1-4 tuần) để team hoàn thành một lượng công việc cam kết — khung thời gian lặp</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
+        <v>Việc viết tài liệu thiết kế chi tiết kéo dài trong 3 tháng đầu dự án — giai đoạn thiết kế đặc tả</v>
+      </c>
+      <c r="H4" t="str">
         <v>Một cuộc họp khẩn cấp khi dự án gặp sự cố nghiêm trọng trên môi trường production — họp xử lý khủng hoảng</v>
       </c>
-      <c r="G4" t="str">
-        <v>Quy trình kiểm thử hiệu năng tải trang web trước khi bàn giao cho khách hàng — kiểm thử tải</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Việc viết tài liệu thiết kế chi tiết kéo dài trong 3 tháng đầu dự án — giai đoạn thiết kế đặc tả</v>
-      </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +540,19 @@
         <v>User Story là công cụ mô tả tính năng ngắn gọn, được viết từ góc nhìn và ngôn ngữ của người dùng cuối để mô tả giá trị họ mong muốn.</v>
       </c>
       <c r="E5" t="str">
+        <v>Kiểm thử viên chịu trách nhiệm tìm lỗi trong hệ thống — góc nhìn kiểm thử viên</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Giám đốc dự án quản lý chi phí và tiến độ chung — góc nhìn quản lý</v>
+      </c>
+      <c r="G5" t="str">
         <v>Người dùng cuối hoặc khách hàng sử dụng sản phẩm — góc nhìn người dùng</v>
       </c>
-      <c r="F5" t="str">
+      <c r="H5" t="str">
         <v>Lập trình viên chịu trách nhiệm viết mã nguồn cho tính năng — góc nhìn nhà phát triển</v>
       </c>
-      <c r="G5" t="str">
-        <v>Kiểm thử viên chịu trách nhiệm tìm lỗi trong hệ thống — góc nhìn kiểm thử viên</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Giám đốc dự án quản lý chi phí và tiến độ chung — góc nhìn quản lý</v>
-      </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -572,13 +572,13 @@
         <v>Định nghĩa các tiêu chuẩn chất lượng bắt buộc để một phần việc được coi là hoàn thành — tiêu chuẩn chất lượng</v>
       </c>
       <c r="F6" t="str">
+        <v>Định nghĩa tiến độ thời gian cần thiết để hoàn thành toàn bộ dự án — tiến độ dự án</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Bảng phân chia công việc cho từng thành viên trong cuộc họp Daily Scrum — bảng phân chia tác vụ</v>
+      </c>
+      <c r="H6" t="str">
         <v>Danh sách các công việc chưa được làm trong Sprint hiện tại — danh sách backlog</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Định nghĩa tiến độ thời gian cần thiết để hoàn thành toàn bộ dự án — tiến độ dự án</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Bảng phân chia công việc cho từng thành viên trong cuộc họp Daily Scrum — bảng phân chia tác vụ</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -601,13 +601,13 @@
         <v>Các thành viên chia sẻ những gì đã làm, sẽ làm và các khó khăn gặp phải — đồng bộ hóa tiến độ</v>
       </c>
       <c r="F7" t="str">
+        <v>BA và PO ngồi viết lại toàn bộ tài liệu đặc tả yêu cầu người dùng — viết đặc tả</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Quản lý dự án phê bình các thành viên làm việc chậm tiến độ — đánh giá nhân sự</v>
+      </c>
+      <c r="H7" t="str">
         <v>Lập trình viên demo trực tiếp các tính năng đã code cho khách hàng duyệt — duyệt tính năng</v>
-      </c>
-      <c r="G7" t="str">
-        <v>BA và PO ngồi viết lại toàn bộ tài liệu đặc tả yêu cầu người dùng — viết đặc tả</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Quản lý dự án phê bình các thành viên làm việc chậm tiến độ — đánh giá nhân sự</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -656,19 +656,19 @@
         <v>Product Owner (PO) chịu trách nhiệm quản lý Product Backlog, bao gồm việc viết, sắp xếp và tối ưu hóa thứ tự ưu tiên của các backlog item.</v>
       </c>
       <c r="E9" t="str">
+        <v>Project Manager (PM) — người chịu trách nhiệm về tiến độ và chi phí</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Lead Developer — người chịu trách nhiệm về kiến trúc kỹ thuật</v>
+      </c>
+      <c r="G9" t="str">
         <v>Product Owner (PO) — người chịu trách nhiệm về giá trị sản phẩm</v>
       </c>
-      <c r="F9" t="str">
+      <c r="H9" t="str">
         <v>Scrum Master — người điều phối quy trình Scrum</v>
       </c>
-      <c r="G9" t="str">
-        <v>Lead Developer — người chịu trách nhiệm về kiến trúc kỹ thuật</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Project Manager (PM) — người chịu trách nhiệm về tiến độ và chi phí</v>
-      </c>
       <c r="I9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -685,7 +685,7 @@
         <v>Yêu cầu chưa đạt DoD không được coi là hoàn thành. Nó phải được đưa lại vào Product Backlog để PO sắp xếp lại độ ưu tiên và không được tính vào Velocity của sprint đó.</v>
       </c>
       <c r="E10" t="str">
-        <v>Chuyển User Story đó về Product Backlog và không tính vào Velocity của Sprint hiện tại — xử lý story dang dở</v>
+        <v>Yêu cầu QA ký biên bản nghiệm thu tạm thời để báo cáo tiến độ đẹp cho khách hàng — gian lận báo cáo</v>
       </c>
       <c r="F10" t="str">
         <v>Vẫn tính là hoàn thành và đưa lên production, sau đó sửa lỗi sau ở Sprint tiếp theo — bàn giao ép buộc</v>
@@ -694,10 +694,10 @@
         <v>Chia đôi Story Point của nó và tính một nửa điểm cho Sprint hiện tại — chia điểm công việc</v>
       </c>
       <c r="H10" t="str">
-        <v>Yêu cầu QA ký biên bản nghiệm thu tạm thời để báo cáo tiến độ đẹp cho khách hàng — gian lận báo cáo</v>
+        <v>Chuyển User Story đó về Product Backlog và không tính vào Velocity của Sprint hiện tại — xử lý story dang dở</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +714,19 @@
         <v>Planning Poker sử dụng dãy số Fibonacci trên các thẻ bài. Các thành viên bỏ phiếu đồng thời để tránh bị ảnh hưởng bởi ý kiến người khác, sau đó thảo luận để đạt được sự đồng thuận.</v>
       </c>
       <c r="E11" t="str">
+        <v>Bốc thăm ngẫu nhiên để chọn ra số điểm cho từng User Story — ước lượng ngẫu nhiên</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Lập trình viên nào xung phong làm task đó sẽ tự quyết định điểm số — ước lượng cá nhân</v>
+      </c>
+      <c r="G11" t="str">
         <v>Đồng thuận tập thể thông qua thảo luận và bỏ phiếu ẩn danh bằng các quân bài Fibonacci — ước lượng đồng thuận</v>
       </c>
-      <c r="F11" t="str">
+      <c r="H11" t="str">
         <v>Quản lý dự án tự áp đặt điểm số dựa trên kinh nghiệm cá nhân của mình — ước lượng đơn phương</v>
       </c>
-      <c r="G11" t="str">
-        <v>Lập trình viên nào xung phong làm task đó sẽ tự quyết định điểm số — ước lượng cá nhân</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Bốc thăm ngẫu nhiên để chọn ra số điểm cho từng User Story — ước lượng ngẫu nhiên</v>
-      </c>
       <c r="I11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -743,19 +743,19 @@
         <v>Epic là một khối công việc/yêu cầu lớn chưa thể ước lượng chi tiết. Epic cần được phân rã thành các User Story nhỏ hơn, tuân thủ tiêu chuẩn INVEST để vừa vào một Sprint.</v>
       </c>
       <c r="E12" t="str">
+        <v>Epic chỉ dùng cho kiểm thử tự động; còn User Story chỉ dùng cho kiểm thử thủ công — phân chia công cụ</v>
+      </c>
+      <c r="F12" t="str">
         <v>Epic là một yêu cầu lớn, khái quát; được phân rã thành nhiều User Story nhỏ có thể hoàn thành trong một Sprint — phân cấp yêu cầu</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
         <v>Epic là tài liệu đặc tả kỹ thuật; còn User Story là mã nguồn lập trình thực tế — phân chia kỹ thuật</v>
       </c>
-      <c r="G12" t="str">
+      <c r="H12" t="str">
         <v>Epic do khách hàng viết; còn User Story do lập trình viên tự viết khi code — phân chia tác giả</v>
       </c>
-      <c r="H12" t="str">
-        <v>Epic chỉ dùng cho kiểm thử tự động; còn User Story chỉ dùng cho kiểm thử thủ công — phân chia công cụ</v>
-      </c>
       <c r="I12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -775,13 +775,13 @@
         <v>Tổng số Story Points của các User Story đạt DoD mà team hoàn thành được trong một Sprint — năng suất trung bình</v>
       </c>
       <c r="F13" t="str">
-        <v>Tốc độ tải trang và phản hồi của hệ thống phần mềm trên máy chủ — tốc độ hệ thống</v>
+        <v>Số lượng tính năng mới được PO thêm vào Product Backlog trong một tuần — tốc độ thêm yêu cầu</v>
       </c>
       <c r="G13" t="str">
         <v>Tổng số giờ mà các lập trình viên đã OT (làm thêm giờ) trong Sprint đó — giờ làm việc</v>
       </c>
       <c r="H13" t="str">
-        <v>Số lượng tính năng mới được PO thêm vào Product Backlog trong một tuần — tốc độ thêm yêu cầu</v>
+        <v>Tốc độ tải trang và phản hồi của hệ thống phần mềm trên máy chủ — tốc độ hệ thống</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -804,13 +804,13 @@
         <v>Đề xuất dành nửa ngày họp Backlog Refinement trước khi chốt scope Sprint để tránh rủi ro ước lượng sai — làm mịn backlog</v>
       </c>
       <c r="F14" t="str">
+        <v>Hủy bỏ toàn bộ Sprint hiện tại và cho team nghỉ ngơi cho đến khi tài liệu sẵn sàng — trì hoãn dự án</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Yêu cầu Scrum Master tự viết Acceptance Criteria thay cho BA và PO — đùn đẩy công việc</v>
+      </c>
+      <c r="H14" t="str">
         <v>Ép buộc team ước lượng đại khái và tiến hành làm, có gì mập mờ sẽ giải thích sau khi code — chấp nhận rủi ro</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Hủy bỏ toàn bộ Sprint hiện tại và cho team nghỉ ngơi cho đến khi tài liệu sẵn sàng — trì hoãn dự án</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Yêu cầu Scrum Master tự viết Acceptance Criteria thay cho BA và PO — đùn đẩy công việc</v>
       </c>
       <c r="I14">
         <v>1</v>
@@ -830,7 +830,7 @@
         <v>Trong INVEST, "V" là Valuable. Mọi câu chuyện người dùng phải đem lại giá trị hữu ích cho khách hàng hoặc người dùng cuối, không viết các story thuần kỹ thuật không có giá trị nghiệp vụ.</v>
       </c>
       <c r="E15" t="str">
-        <v>Valuable — Mỗi User Story được viết ra phải mang lại giá trị thực tế cho người dùng hoặc doanh nghiệp — giá trị nghiệp vụ</v>
+        <v>Visual — Giao diện của Story phải được vẽ đẹp mắt bằng các công cụ thiết kế chuyên nghiệp — tính trực quan</v>
       </c>
       <c r="F15" t="str">
         <v>Verifiable — Story phải được cài đặt thành công trên môi trường của khách hàng — xác thực cài đặt</v>
@@ -839,10 +839,10 @@
         <v>Variable — Nội dung yêu cầu có thể thay đổi liên tục trong suốt quá trình code — tính biến động</v>
       </c>
       <c r="H15" t="str">
-        <v>Visual — Giao diện của Story phải được vẽ đẹp mắt bằng các công cụ thiết kế chuyên nghiệp — tính trực quan</v>
+        <v>Valuable — Mỗi User Story được viết ra phải mang lại giá trị thực tế cho người dùng hoặc doanh nghiệp — giá trị nghiệp vụ</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -859,19 +859,19 @@
         <v>Backlog Refinement là hoạt động liên tục giúp chuẩn bị sẵn sàng các backlog item cho sprint tiếp theo bằng cách làm rõ chi tiết, viết AC và ước lượng sơ bộ.</v>
       </c>
       <c r="E16" t="str">
-        <v>Diễn ra trong suốt Sprint để PO, BA và team thảo luận, làm rõ và ước lượng trước các story cho các sprint sau — chuẩn bị yêu cầu</v>
+        <v>Diễn ra ngay trên môi trường Production để vá các lỗi bảo mật khẩn cấp — vá lỗi hệ thống</v>
       </c>
       <c r="F16" t="str">
         <v>Diễn ra vào ngày cuối cùng của Sprint để chấm điểm hiệu suất của từng lập trình viên — đánh giá nhân sự</v>
       </c>
       <c r="G16" t="str">
-        <v>Diễn ra ngay trên môi trường Production để vá các lỗi bảo mật khẩn cấp — vá lỗi hệ thống</v>
+        <v>Diễn ra trước khi ký hợp đồng dự án để chốt tổng chi phí với khách hàng — báo giá dự án</v>
       </c>
       <c r="H16" t="str">
-        <v>Diễn ra trước khi ký hợp đồng dự án để chốt tổng chi phí với khách hàng — báo giá dự án</v>
+        <v>Diễn ra trong suốt Sprint để PO, BA và team thảo luận, làm rõ và ước lượng trước các story cho các sprint sau — chuẩn bị yêu cầu</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -891,13 +891,13 @@
         <v>Vi phạm tiêu chí Testable (Không thể kiểm thử) vì từ "chạy nhanh hơn" quá mơ hồ, không có chỉ số đo lường — thiếu tính định lượng</v>
       </c>
       <c r="F17" t="str">
-        <v>Vi phạm tiêu chí Independent vì quản trị viên không thể thực hiện các hành động độc lập — phụ thuộc vai trò</v>
+        <v>Vi phạm tiêu chí Valuable vì việc tiết kiệm thời gian không mang lại giá trị cho doanh nghiệp — giá trị thấp</v>
       </c>
       <c r="G17" t="str">
         <v>Vi phạm tiêu chí Small vì đây là một yêu cầu quá nhỏ không cần viết thành User Story — kích thước quá nhỏ</v>
       </c>
       <c r="H17" t="str">
-        <v>Vi phạm tiêu chí Valuable vì việc tiết kiệm thời gian không mang lại giá trị cho doanh nghiệp — giá trị thấp</v>
+        <v>Vi phạm tiêu chí Independent vì quản trị viên không thể thực hiện các hành động độc lập — phụ thuộc vai trò</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -917,19 +917,19 @@
         <v>Sprint Review là buổi họp cuối Sprint để team trình bày kết quả công việc đã hoàn thành đạt DoD cho khách hàng/stakeholder xem và lấy ý kiến phản hồi.</v>
       </c>
       <c r="E18" t="str">
-        <v>Trình bày phần tăng trưởng sản phẩm (Increment) đã hoàn thành cho các bên liên quan và nhận phản hồi đóng góp — demo và nhận feedback</v>
+        <v>Đứng ra phân tích lỗi và chỉ trích các thành viên làm phát sinh bug trong sprint — tìm người chịu trách nhiệm</v>
       </c>
       <c r="F18" t="str">
         <v>Thực hiện viết code bổ sung cho các tính năng chưa kịp hoàn thành trong sprint — chạy nước rút code</v>
       </c>
       <c r="G18" t="str">
-        <v>Đứng ra phân tích lỗi và chỉ trích các thành viên làm phát sinh bug trong sprint — tìm người chịu trách nhiệm</v>
+        <v>Trình bày phần tăng trưởng sản phẩm (Increment) đã hoàn thành cho các bên liên quan và nhận phản hồi đóng góp — demo và nhận feedback</v>
       </c>
       <c r="H18" t="str">
         <v>Lên danh sách phân chia công việc chi tiết cho sprint tiếp theo — lập kế hoạch tương lai</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -946,19 +946,19 @@
         <v>Để tuân thủ tiêu chuẩn INVEST (I - Independent), team có thể sử dụng Mock API/Stubs để kiểm thử logic nghiệp vụ của story mà không bị block bởi các dependencies bên ngoài.</v>
       </c>
       <c r="E19" t="str">
-        <v>Đề xuất team phát triển tạo mock API (dữ liệu giả lập) để tự hoàn thành story độc lập, tránh bị nghẽn tiến độ — giải quyết phụ thuộc</v>
+        <v>Trì hoãn story đó vô thời hạn cho đến khi team kia bàn giao xong API thực tế mới bắt đầu làm — trì hoãn thụ động</v>
       </c>
       <c r="F19" t="str">
-        <v>Trì hoãn story đó vô thời hạn cho đến khi team kia bàn giao xong API thực tế mới bắt đầu làm — trì hoãn thụ động</v>
+        <v>Thay đổi thiết kế để loại bỏ hoàn toàn tính năng gọi API đó ra khỏi hệ thống phần mềm — cắt giảm tính năng</v>
       </c>
       <c r="G19" t="str">
         <v>Yêu cầu lập trình viên của team mình nhảy sang viết hộ code API cho team đối tác — can thiệp nhân sự</v>
       </c>
       <c r="H19" t="str">
-        <v>Thay đổi thiết kế để loại bỏ hoàn toàn tính năng gọi API đó ra khỏi hệ thống phần mềm — cắt giảm tính năng</v>
+        <v>Đề xuất team phát triển tạo mock API (dữ liệu giả lập) để tự hoàn thành story độc lập, tránh bị nghẽn tiến độ — giải quyết phụ thuộc</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -975,19 +975,19 @@
         <v>Cắt lát dọc (Vertical Slicing) tạo ra các câu chuyện người dùng hoàn chỉnh từ giao diện đến database. Nhờ đó, người dùng có thể tương tác và phản hồi ngay lập tức, thay vì phải chờ tất cả các tầng kỹ thuật ghép lại.</v>
       </c>
       <c r="E20" t="str">
-        <v>Mỗi story nhỏ đều đi qua đầy đủ các tầng UI-Logic-DB, đảm bảo bàn giao được giá trị chạy thử được cho người dùng — giá trị hoàn chỉnh</v>
+        <v>Giảm thiểu tối đa số lượng test case mà QA cần phải viết cho hệ thống — giảm tải kiểm thử</v>
       </c>
       <c r="F20" t="str">
         <v>Cho phép chia công việc theo kỹ năng chuyên môn: Dev Backend làm riêng, Dev Frontend làm riêng mà không cần nói chuyện — tách biệt công việc</v>
       </c>
       <c r="G20" t="str">
-        <v>Giảm thiểu tối đa số lượng test case mà QA cần phải viết cho hệ thống — giảm tải kiểm thử</v>
+        <v>Mỗi story nhỏ đều đi qua đầy đủ các tầng UI-Logic-DB, đảm bảo bàn giao được giá trị chạy thử được cho người dùng — giá trị hoàn chỉnh</v>
       </c>
       <c r="H20" t="str">
         <v>Giúp tiết kiệm dung lượng lưu trữ cơ sở dữ liệu trên máy chủ Cloud — tối ưu bộ nhớ</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1004,19 +1004,19 @@
         <v>Spillage xảy ra liên tục chứng tỏ team chưa nắm vững Velocity thực tế hoặc lập kế hoạch Sprint Planning dựa trên cảm tính, hoặc đưa các yêu cầu chưa sẵn sàng (DoR) vào sprint dẫn đến phát sinh công việc ngoài dự kiến.</v>
       </c>
       <c r="E21" t="str">
-        <v>Team đang ước lượng quá lạc quan, hoặc cam kết vượt quá năng lực thực tế (Velocity), hoặc các story đưa vào sprint chưa đạt DoR — vấn đề lập kế hoạch</v>
+        <v>Khách hàng gửi quá ít yêu cầu thay đổi trong quá trình chạy sprint — thiếu yêu cầu từ khách hàng</v>
       </c>
       <c r="F21" t="str">
         <v>Máy chủ của công ty quá yếu khiến lập trình viên mất nhiều thời gian biên dịch code — vấn đề phần cứng</v>
       </c>
       <c r="G21" t="str">
-        <v>Khách hàng gửi quá ít yêu cầu thay đổi trong quá trình chạy sprint — thiếu yêu cầu từ khách hàng</v>
+        <v>Team đang ước lượng quá lạc quan, hoặc cam kết vượt quá năng lực thực tế (Velocity), hoặc các story đưa vào sprint chưa đạt DoR — vấn đề lập kế hoạch</v>
       </c>
       <c r="H21" t="str">
         <v>Quy trình Definition of Done (DoD) đang quá lỏng lẻo khiến việc nghiệm thu diễn ra quá nhanh — DoD lỏng lẻo</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1033,19 +1033,19 @@
         <v>Sự lệch pha giữa User Story và kỳ vọng kinh doanh thường do BA viết câu chuyện quá máy móc hoặc thiếu ngữ cảnh thực tế của người dùng. BA cần cải tiến cách viết Acceptance Criteria (như dùng BDD/Gherkin) để khách hàng dễ hiểu và duyệt trước.</v>
       </c>
       <c r="E22" t="str">
-        <v>Cải tiến hoạt động khơi gợi yêu cầu và xem xét lại cách viết Acceptance Criteria; sử dụng kịch bản nghiệp vụ thực tế thay vì các mô tả kỹ thuật khô khan — tăng chất lượng đặc tả</v>
+        <v>Tăng gấp đôi số lượng Story Point ước lượng cho mỗi tính năng để có thêm thời gian sửa đổi — kéo dài thời gian</v>
       </c>
       <c r="F22" t="str">
         <v>Yêu cầu khách hàng tự viết User Story và chịu trách nhiệm nếu phần mềm chạy không đúng ý — chuyển giao trách nhiệm</v>
       </c>
       <c r="G22" t="str">
-        <v>Tăng gấp đôi số lượng Story Point ước lượng cho mỗi tính năng để có thêm thời gian sửa đổi — kéo dài thời gian</v>
+        <v>Cải tiến hoạt động khơi gợi yêu cầu và xem xét lại cách viết Acceptance Criteria; sử dụng kịch bản nghiệp vụ thực tế thay vì các mô tả kỹ thuật khô khan — tăng chất lượng đặc tả</v>
       </c>
       <c r="H22" t="str">
         <v>Cấm khách hàng tham gia vào buổi họp Sprint Review để tránh nhận ý kiến phản hồi tiêu cực — chặn feedback</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1062,7 +1062,7 @@
         <v>Trong các dự án quy mô lớn (như SAFe), PM quản lý định hướng vĩ mô (tầm nhìn, roadmap). PO sở hữu backlog của team. BA đóng vai trò phân tích nghiệp vụ chi tiết, viết User Stories và làm cầu nối kỹ thuật hàng ngày cho team.</v>
       </c>
       <c r="E23" t="str">
-        <v>PM định nghĩa tầm nhìn sản phẩm cấp cao (Features/Roadmap); PO quản lý backlog của Scrum Team; BA hỗ trợ PO đặc tả chi tiết User Story và làm rõ nghiệp vụ cho Dev — phân cấp quản lý yêu cầu</v>
+        <v>PM và PO chỉ làm quản lý nhân sự, toàn bộ việc định hướng sản phẩm do BA chịu trách nhiệm độc lập — BA định hướng</v>
       </c>
       <c r="F23" t="str">
         <v>BA thay thế hoàn toàn vai trò của PO và PM để tự quyết định toàn bộ kiến trúc phần mềm và ký hợp đồng dự án — tập trung quyền lực</v>
@@ -1071,10 +1071,10 @@
         <v>BA chỉ làm nhiệm vụ vẽ wireframe và thiết kế giao diện đồ họa cho dự án chứ không tham gia viết yêu cầu — thuần UI/UX</v>
       </c>
       <c r="H23" t="str">
-        <v>PM và PO chỉ làm quản lý nhân sự, toàn bộ việc định hướng sản phẩm do BA chịu trách nhiệm độc lập — BA định hướng</v>
+        <v>PM định nghĩa tầm nhìn sản phẩm cấp cao (Features/Roadmap); PO quản lý backlog của Scrum Team; BA hỗ trợ PO đặc tả chi tiết User Story và làm rõ nghiệp vụ cho Dev — phân cấp quản lý yêu cầu</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1091,19 +1091,19 @@
         <v>Định dạng Given-When-Then của ngôn ngữ Gherkin giúp cụ thể hóa hành vi hệ thống dưới dạng kịch bản chạy được. Nó giúp thu hẹp khoảng cách hiểu giữa nghiệp vụ (BA/khách hàng) và kỹ thuật (Dev/QA), làm tiền đề cho kiểm thử tự động.</v>
       </c>
       <c r="E24" t="str">
+        <v>Để đảm bảo giao diện người dùng hiển thị đúng các màu sắc và font chữ quy định — ràng buộc giao diện</v>
+      </c>
+      <c r="F24" t="str">
         <v>Để tạo ra một ngôn ngữ chung duy nhất (Ubiquitous Language) mà cả khách hàng, Dev và QA đều hiểu thống nhất, đồng thời có thể tự động hóa thành test scripts — ngôn ngữ chung nhất quán</v>
-      </c>
-      <c r="F24" t="str">
-        <v>Để ép buộc lập trình viên phải sử dụng cấu trúc rẽ nhánh IF-THEN-ELSE khi viết mã nguồn — ràng buộc cấu trúc code</v>
       </c>
       <c r="G24" t="str">
         <v>Để giảm thiểu thời gian BA phải viết tài liệu giải thích nghiệp vụ cho khách hàng — tiết kiệm thời gian BA</v>
       </c>
       <c r="H24" t="str">
-        <v>Để đảm bảo giao diện người dùng hiển thị đúng các màu sắc và font chữ quy định — ràng buộc giao diện</v>
+        <v>Để ép buộc lập trình viên phải sử dụng cấu trúc rẽ nhánh IF-THEN-ELSE khi viết mã nguồn — ràng buộc cấu trúc code</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1149,19 +1149,19 @@
         <v>BA là nhà phân tích. Khi có thay đổi giữa chừng, BA phải nhanh chóng làm rõ tác động (về scope, rủi ro, nỗ lực) để cung cấp bức tranh toàn cảnh cho PO đưa ra quyết định sáng suốt và bảo vệ Sprint Goal của team.</v>
       </c>
       <c r="E26" t="str">
+        <v>Tự ý hủy bỏ sprint hiện tại mà không cần sự đồng ý của Scrum Team và PO — lạm quyền quyết định</v>
+      </c>
+      <c r="F26" t="str">
         <v>Hỗ trợ PO thực hiện phân tích tác động (Impact Analysis) của thay đổi, đưa ra các rủi ro về mặt kỹ thuật và tiến độ để PO có cơ sở thương lượng trì hoãn thay đổi sang Sprint sau — điều phối và phân tích tác động</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Lập tức đồng ý với Stakeholders và yêu cầu Dev làm thêm giờ để kịp tiến độ ban đầu mà không cần báo cáo PO — thỏa hiệp thụ động</v>
       </c>
       <c r="G26" t="str">
         <v>Yêu cầu Scrum Master đứng ra kỷ luật PO vì đã vi phạm nguyên tắc Scrum — kỷ luật nội bộ</v>
       </c>
       <c r="H26" t="str">
-        <v>Tự ý hủy bỏ sprint hiện tại mà không cần sự đồng ý của Scrum Team và PO — lạm quyền quyết định</v>
+        <v>Lập tức đồng ý với Stakeholders và yêu cầu Dev làm thêm giờ để kịp tiến độ ban đầu mà không cần báo cáo PO — thỏa hiệp thụ động</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
